--- a/artfynd/A 28206-2026 artfynd.xlsx
+++ b/artfynd/A 28206-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -779,10 +779,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>64350423</v>
+        <v>135183638</v>
       </c>
       <c r="B3" t="n">
-        <v>80336</v>
+        <v>96410</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -790,40 +790,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>2812</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bredberget, Vb</t>
+          <t>Lidberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>772353</v>
+        <v>772590</v>
       </c>
       <c r="R3" t="n">
-        <v>7187187</v>
+        <v>7187471</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,12 +844,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2012-06-18</t>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2012-06-18</t>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -870,15 +874,1331 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135183630</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lidberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>772632</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7187753</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>64350423</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bredberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>772353</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7187187</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2012-06-18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2012-06-18</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Patrik Nygren</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Patrik Nygren</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135183627</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80382</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lidberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>772562</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7187914</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135183624</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lidberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>772568</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7187972</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135183632</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lidberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>772496</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7187337</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Bilder</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135183625</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80500</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lidberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>772568</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7187972</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135183634</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lidberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>772553</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7187362</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135183633</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lidberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>772501</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7187314</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska barksprätt bild</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135183635</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lidberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>772553</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7187434</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Läte</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135183626</v>
+      </c>
+      <c r="B13" t="n">
+        <v>106324</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lidberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>772563</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7187954</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135183631</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98249</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lidberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>772532</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7187488</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135183637</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98249</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lidberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>772567</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7187458</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28206-2026 artfynd.xlsx
+++ b/artfynd/A 28206-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -776,6 +781,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64350410</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135183638</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135183630</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1093,6 +1113,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64350423</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1200,6 +1225,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135183627</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1307,6 +1337,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135183624</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1419,6 +1454,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135183632</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1526,6 +1566,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135183625</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1638,6 +1683,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135183634</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1758,6 +1808,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135183633</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1878,6 +1933,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135183635</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1985,6 +2045,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135183626</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2092,6 +2157,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135183631</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2199,8 +2269,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135183637</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 28206-2026 artfynd.xlsx
+++ b/artfynd/A 28206-2026 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>135183638</v>
       </c>
       <c r="B3" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>135183630</v>
       </c>
       <c r="B4" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>135183627</v>
       </c>
       <c r="B6" t="n">
-        <v>80382</v>
+        <v>80420</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>135183624</v>
       </c>
       <c r="B7" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>135183632</v>
       </c>
       <c r="B8" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>135183625</v>
       </c>
       <c r="B9" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>135183634</v>
       </c>
       <c r="B10" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>135183633</v>
       </c>
       <c r="B11" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>135183635</v>
       </c>
       <c r="B12" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>135183626</v>
       </c>
       <c r="B13" t="n">
-        <v>106324</v>
+        <v>106379</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>135183631</v>
       </c>
       <c r="B14" t="n">
-        <v>98249</v>
+        <v>98293</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>135183637</v>
       </c>
       <c r="B15" t="n">
-        <v>98249</v>
+        <v>98293</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 28206-2026 artfynd.xlsx
+++ b/artfynd/A 28206-2026 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>135183638</v>
       </c>
       <c r="B3" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>135183630</v>
       </c>
       <c r="B4" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>135183627</v>
       </c>
       <c r="B6" t="n">
-        <v>80420</v>
+        <v>80447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>135183624</v>
       </c>
       <c r="B7" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>135183632</v>
       </c>
       <c r="B8" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>135183625</v>
       </c>
       <c r="B9" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>135183626</v>
       </c>
       <c r="B13" t="n">
-        <v>106379</v>
+        <v>106406</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>135183631</v>
       </c>
       <c r="B14" t="n">
-        <v>98293</v>
+        <v>98320</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>135183637</v>
       </c>
       <c r="B15" t="n">
-        <v>98293</v>
+        <v>98320</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 28206-2026 artfynd.xlsx
+++ b/artfynd/A 28206-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>64350423</v>
+        <v>135183638</v>
       </c>
       <c r="B3" t="n">
-        <v>80336</v>
+        <v>96486</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,40 +800,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>2812</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bredberget, Vb</t>
+          <t>Lidberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>772353</v>
+        <v>772590</v>
       </c>
       <c r="R3" t="n">
-        <v>7187187</v>
+        <v>7187471</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,12 +854,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2012-06-18</t>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2012-06-18</t>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -880,18 +884,1442 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135183638</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135183630</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93345</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lidberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>772632</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7187753</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135183630</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>64350423</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bredberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>772353</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7187187</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2012-06-18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2012-06-18</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Patrik Nygren</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Patrik Nygren</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr">
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/64350423</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135183627</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80450</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lidberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>772562</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7187914</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135183627</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135183624</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80556</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lidberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>772568</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7187972</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135183624</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135183632</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80556</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lidberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>772496</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7187337</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Bilder</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135183632</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135183625</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80568</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lidberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>772568</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7187972</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135183625</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135183634</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lidberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>772553</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7187362</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135183634</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135183633</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lidberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>772501</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7187314</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska barksprätt bild</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135183633</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135183635</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lidberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>772553</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7187434</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Läte</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135183635</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135183626</v>
+      </c>
+      <c r="B13" t="n">
+        <v>106411</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lidberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>772563</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7187954</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135183626</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135183631</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98325</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lidberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>772532</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7187488</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135183631</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135183637</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98325</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lidberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>772567</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7187458</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135183637</t>
         </is>
       </c>
     </row>
@@ -899,6 +2327,18 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28206-2026 artfynd.xlsx
+++ b/artfynd/A 28206-2026 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>135183638</v>
       </c>
       <c r="B3" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>135183630</v>
       </c>
       <c r="B4" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>135183626</v>
       </c>
       <c r="B13" t="n">
-        <v>106411</v>
+        <v>106413</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>135183631</v>
       </c>
       <c r="B14" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>135183637</v>
       </c>
       <c r="B15" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 28206-2026 artfynd.xlsx
+++ b/artfynd/A 28206-2026 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>135183638</v>
       </c>
       <c r="B3" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>135183630</v>
       </c>
       <c r="B4" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>135183627</v>
       </c>
       <c r="B6" t="n">
-        <v>80450</v>
+        <v>80452</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>135183624</v>
       </c>
       <c r="B7" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>135183632</v>
       </c>
       <c r="B8" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>135183625</v>
       </c>
       <c r="B9" t="n">
-        <v>80568</v>
+        <v>80570</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135183634</v>
       </c>
       <c r="B10" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>135183633</v>
       </c>
       <c r="B11" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>135183635</v>
       </c>
       <c r="B12" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>135183626</v>
       </c>
       <c r="B13" t="n">
-        <v>106413</v>
+        <v>106433</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>135183631</v>
       </c>
       <c r="B14" t="n">
-        <v>98327</v>
+        <v>98344</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>135183637</v>
       </c>
       <c r="B15" t="n">
-        <v>98327</v>
+        <v>98344</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 28206-2026 artfynd.xlsx
+++ b/artfynd/A 28206-2026 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>135183638</v>
       </c>
       <c r="B3" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>135183630</v>
       </c>
       <c r="B4" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>135183627</v>
       </c>
       <c r="B6" t="n">
-        <v>80452</v>
+        <v>80453</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>135183624</v>
       </c>
       <c r="B7" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>135183632</v>
       </c>
       <c r="B8" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>135183625</v>
       </c>
       <c r="B9" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>135183626</v>
       </c>
       <c r="B13" t="n">
-        <v>106433</v>
+        <v>106435</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>135183631</v>
       </c>
       <c r="B14" t="n">
-        <v>98344</v>
+        <v>98345</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>135183637</v>
       </c>
       <c r="B15" t="n">
-        <v>98344</v>
+        <v>98345</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 28206-2026 artfynd.xlsx
+++ b/artfynd/A 28206-2026 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>135183638</v>
       </c>
       <c r="B3" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>135183630</v>
       </c>
       <c r="B4" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>135183626</v>
       </c>
       <c r="B13" t="n">
-        <v>106435</v>
+        <v>106436</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>135183631</v>
       </c>
       <c r="B14" t="n">
-        <v>98345</v>
+        <v>98346</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>135183637</v>
       </c>
       <c r="B15" t="n">
-        <v>98345</v>
+        <v>98346</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 28206-2026 artfynd.xlsx
+++ b/artfynd/A 28206-2026 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>135183638</v>
       </c>
       <c r="B3" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>135183630</v>
       </c>
       <c r="B4" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>135183627</v>
       </c>
       <c r="B6" t="n">
-        <v>80453</v>
+        <v>80454</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>135183624</v>
       </c>
       <c r="B7" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>135183632</v>
       </c>
       <c r="B8" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>135183625</v>
       </c>
       <c r="B9" t="n">
-        <v>80571</v>
+        <v>80572</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135183634</v>
       </c>
       <c r="B10" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>135183633</v>
       </c>
       <c r="B11" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>135183635</v>
       </c>
       <c r="B12" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>135183626</v>
       </c>
       <c r="B13" t="n">
-        <v>106436</v>
+        <v>106437</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>135183631</v>
       </c>
       <c r="B14" t="n">
-        <v>98346</v>
+        <v>98347</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>135183637</v>
       </c>
       <c r="B15" t="n">
-        <v>98346</v>
+        <v>98347</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 28206-2026 artfynd.xlsx
+++ b/artfynd/A 28206-2026 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>135183638</v>
       </c>
       <c r="B3" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>135183630</v>
       </c>
       <c r="B4" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>135183627</v>
       </c>
       <c r="B6" t="n">
-        <v>80454</v>
+        <v>80458</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>135183624</v>
       </c>
       <c r="B7" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>135183632</v>
       </c>
       <c r="B8" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>135183625</v>
       </c>
       <c r="B9" t="n">
-        <v>80572</v>
+        <v>80576</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135183634</v>
       </c>
       <c r="B10" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>135183633</v>
       </c>
       <c r="B11" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>135183635</v>
       </c>
       <c r="B12" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>135183626</v>
       </c>
       <c r="B13" t="n">
-        <v>106437</v>
+        <v>106443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>135183631</v>
       </c>
       <c r="B14" t="n">
-        <v>98347</v>
+        <v>98353</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>135183637</v>
       </c>
       <c r="B15" t="n">
-        <v>98347</v>
+        <v>98353</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 28206-2026 artfynd.xlsx
+++ b/artfynd/A 28206-2026 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>135183638</v>
       </c>
       <c r="B3" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>135183630</v>
       </c>
       <c r="B4" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>135183627</v>
       </c>
       <c r="B6" t="n">
-        <v>80458</v>
+        <v>80459</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>135183624</v>
       </c>
       <c r="B7" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>135183632</v>
       </c>
       <c r="B8" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>135183625</v>
       </c>
       <c r="B9" t="n">
-        <v>80576</v>
+        <v>80577</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135183634</v>
       </c>
       <c r="B10" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>135183633</v>
       </c>
       <c r="B11" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>135183635</v>
       </c>
       <c r="B12" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>135183626</v>
       </c>
       <c r="B13" t="n">
-        <v>106443</v>
+        <v>106444</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>135183631</v>
       </c>
       <c r="B14" t="n">
-        <v>98353</v>
+        <v>98354</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>135183637</v>
       </c>
       <c r="B15" t="n">
-        <v>98353</v>
+        <v>98354</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 28206-2026 artfynd.xlsx
+++ b/artfynd/A 28206-2026 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>135183638</v>
       </c>
       <c r="B3" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>135183630</v>
       </c>
       <c r="B4" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>135183627</v>
       </c>
       <c r="B6" t="n">
-        <v>80459</v>
+        <v>80463</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>135183624</v>
       </c>
       <c r="B7" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>135183632</v>
       </c>
       <c r="B8" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>135183625</v>
       </c>
       <c r="B9" t="n">
-        <v>80577</v>
+        <v>80581</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>135183626</v>
       </c>
       <c r="B13" t="n">
-        <v>106444</v>
+        <v>106455</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>135183631</v>
       </c>
       <c r="B14" t="n">
-        <v>98354</v>
+        <v>98365</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>135183637</v>
       </c>
       <c r="B15" t="n">
-        <v>98354</v>
+        <v>98365</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 28206-2026 artfynd.xlsx
+++ b/artfynd/A 28206-2026 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>135183638</v>
       </c>
       <c r="B3" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>135183630</v>
       </c>
       <c r="B4" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>135183627</v>
       </c>
       <c r="B6" t="n">
-        <v>80463</v>
+        <v>80469</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>135183624</v>
       </c>
       <c r="B7" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>135183632</v>
       </c>
       <c r="B8" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>135183625</v>
       </c>
       <c r="B9" t="n">
-        <v>80581</v>
+        <v>80587</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135183634</v>
       </c>
       <c r="B10" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>135183633</v>
       </c>
       <c r="B11" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>135183635</v>
       </c>
       <c r="B12" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>135183626</v>
       </c>
       <c r="B13" t="n">
-        <v>106455</v>
+        <v>106468</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>135183631</v>
       </c>
       <c r="B14" t="n">
-        <v>98365</v>
+        <v>98378</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>135183637</v>
       </c>
       <c r="B15" t="n">
-        <v>98365</v>
+        <v>98378</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 28206-2026 artfynd.xlsx
+++ b/artfynd/A 28206-2026 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>135183638</v>
       </c>
       <c r="B3" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>135183630</v>
       </c>
       <c r="B4" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>135183626</v>
       </c>
       <c r="B13" t="n">
-        <v>106468</v>
+        <v>106469</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>135183631</v>
       </c>
       <c r="B14" t="n">
-        <v>98378</v>
+        <v>98379</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>135183637</v>
       </c>
       <c r="B15" t="n">
-        <v>98378</v>
+        <v>98379</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
